--- a/data/exports/test-portfolio_intelligence.xlsx
+++ b/data/exports/test-portfolio_intelligence.xlsx
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3963.15</v>
+        <v>3941.7</v>
       </c>
       <c r="C2" t="n">
-        <v>48.9</v>
+        <v>48.74</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>2811</v>
       </c>
       <c r="C3" t="n">
-        <v>34.68</v>
+        <v>34.76</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="C4" t="n">
-        <v>16.42</v>
+        <v>16.51</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1199,13 +1199,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="E2" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0188</v>
+        <v>1.0187</v>
       </c>
     </row>
     <row r="3">
@@ -1229,7 +1229,7 @@
         <v>2361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8048</v>
+        <v>0.8041</v>
       </c>
     </row>
     <row r="4">
@@ -1247,13 +1247,13 @@
         <v>3.25</v>
       </c>
       <c r="D4" t="n">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E4" t="n">
-        <v>447.53</v>
+        <v>443.22</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4607</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="5">
@@ -1271,13 +1271,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="E5" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9745</v>
+        <v>0.9744</v>
       </c>
     </row>
     <row r="6">
@@ -1301,7 +1301,7 @@
         <v>2361</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9019</v>
+        <v>0.9022</v>
       </c>
     </row>
     <row r="7">
@@ -1319,13 +1319,13 @@
         <v>3.25</v>
       </c>
       <c r="D7" t="n">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E7" t="n">
-        <v>447.53</v>
+        <v>443.22</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4607</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="8">
@@ -1343,13 +1343,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="E8" t="n">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6188</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="9">
@@ -1373,7 +1373,7 @@
         <v>2361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7268</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="10">
@@ -1391,13 +1391,13 @@
         <v>3.25</v>
       </c>
       <c r="D10" t="n">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E10" t="n">
-        <v>447.53</v>
+        <v>443.22</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8607</v>
+        <v>0.862</v>
       </c>
     </row>
   </sheetData>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13.32</v>
+        <v>13.36</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2237,19 +2237,19 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>13.32</v>
+        <v>13.36</v>
       </c>
       <c r="L3" t="n">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="M3" t="n">
         <v>553</v>
       </c>
       <c r="N3" t="n">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="O3" t="n">
-        <v>140.87</v>
+        <v>141.59</v>
       </c>
     </row>
     <row r="4">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>610.83</v>
+        <v>610.02</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>213.21</v>
+        <v>213.76</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>431.34</v>
+        <v>433.15</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>264.1</v>
+        <v>262.8</v>
       </c>
       <c r="L7" t="n">
-        <v>3961.5</v>
+        <v>3942</v>
       </c>
       <c r="M7" t="n">
         <v>1896</v>
       </c>
       <c r="N7" t="n">
-        <v>2065.5</v>
+        <v>2046</v>
       </c>
       <c r="O7" t="n">
-        <v>108.94</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="8">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>383.15</v>
+        <v>382.38</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>137.46</v>
+        <v>137.38</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2685,16 +2685,16 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="D2" t="n">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="E2" t="n">
-        <v>7.79</v>
+        <v>7.83</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9745</v>
+        <v>0.9744</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -2730,13 +2730,13 @@
         <v>39.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9019</v>
+        <v>0.9021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7571</v>
+        <v>0.7548</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5625</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="C4" t="n">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="D4" t="n">
-        <v>446.83</v>
+        <v>442.73</v>
       </c>
       <c r="E4" t="n">
-        <v>137.7</v>
+        <v>136.4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4608</v>
+        <v>0.4619</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107.09</v>
+        <v>107.33</v>
       </c>
       <c r="C2" t="n">
         <v>102.39</v>
@@ -2905,7 +2905,7 @@
         <v>100.14</v>
       </c>
       <c r="E2" t="n">
-        <v>35.9</v>
+        <v>36.11</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -2914,13 +2914,13 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8205</v>
+        <v>0.8194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.641</v>
+        <v>0.6389</v>
       </c>
       <c r="J2" t="n">
-        <v>0.831</v>
+        <v>0.8307</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>0.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3655</v>
+        <v>0.3656</v>
       </c>
     </row>
     <row r="3">
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213.22</v>
+        <v>213.8</v>
       </c>
       <c r="C3" t="n">
-        <v>197.47</v>
+        <v>197.48</v>
       </c>
       <c r="D3" t="n">
         <v>187.18</v>
       </c>
       <c r="E3" t="n">
-        <v>62.39</v>
+        <v>62.93</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -2978,13 +2978,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6881</v>
+        <v>0.6854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3761</v>
+        <v>0.3707</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8104</v>
+        <v>0.8096</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3601</v>
+        <v>0.3597</v>
       </c>
     </row>
     <row r="4">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.04</v>
+        <v>12.13</v>
       </c>
       <c r="C4" t="n">
         <v>11.44</v>
@@ -3033,7 +3033,7 @@
         <v>5.86</v>
       </c>
       <c r="E4" t="n">
-        <v>35.8</v>
+        <v>36.01</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3042,13 +3042,13 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>0.642</v>
+        <v>0.6399</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7965</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>16.44</v>
+        <v>16.52</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8356</v>
+        <v>0.8348</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>0.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4321</v>
+        <v>0.4315</v>
       </c>
     </row>
     <row r="5">
@@ -3088,16 +3088,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>497.06</v>
+        <v>495.39</v>
       </c>
       <c r="C5" t="n">
-        <v>309.26</v>
+        <v>309.23</v>
       </c>
       <c r="D5" t="n">
-        <v>232.5</v>
+        <v>232.49</v>
       </c>
       <c r="E5" t="n">
-        <v>76.7</v>
+        <v>76.55</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3106,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6165</v>
+        <v>0.6173</v>
       </c>
       <c r="I5" t="n">
-        <v>0.233</v>
+        <v>0.2345</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7881</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3523</v>
+        <v>0.3525</v>
       </c>
     </row>
     <row r="6">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.31</v>
+        <v>13.36</v>
       </c>
       <c r="C6" t="n">
         <v>9.109999999999999</v>
@@ -3161,7 +3161,7 @@
         <v>6.92</v>
       </c>
       <c r="E6" t="n">
-        <v>59.03</v>
+        <v>59.14</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -3170,13 +3170,13 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7048</v>
+        <v>0.7043</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4097</v>
+        <v>0.4086</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7554</v>
+        <v>0.7551</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>16.44</v>
+        <v>16.52</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8356</v>
+        <v>0.8348</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>0.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0.391</v>
+        <v>0.3906</v>
       </c>
     </row>
     <row r="7">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220.43</v>
+        <v>220.34</v>
       </c>
       <c r="C7" t="n">
         <v>208.21</v>
@@ -3225,7 +3225,7 @@
         <v>204.15</v>
       </c>
       <c r="E7" t="n">
-        <v>40.04</v>
+        <v>40</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -3234,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7998</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5996</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0.6992</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4086</v>
+        <v>0.4087</v>
       </c>
     </row>
     <row r="8">
@@ -3280,16 +3280,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>189.35</v>
+        <v>188.15</v>
       </c>
       <c r="C8" t="n">
-        <v>152.79</v>
+        <v>152.76</v>
       </c>
       <c r="D8" t="n">
-        <v>127</v>
+        <v>126.99</v>
       </c>
       <c r="E8" t="n">
-        <v>43.81</v>
+        <v>42.43</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -3298,13 +3298,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.781</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5619</v>
+        <v>0.5757</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6904</v>
+        <v>0.6924</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3878</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="9">
@@ -3344,16 +3344,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.45999999999999</v>
+        <v>80.39</v>
       </c>
       <c r="C9" t="n">
-        <v>77.51000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="D9" t="n">
         <v>72.2</v>
       </c>
       <c r="E9" t="n">
-        <v>63.91</v>
+        <v>63.2</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -3362,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6804</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3609</v>
+        <v>0.368</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6888</v>
+        <v>0.6898</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>0.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.578</v>
+        <v>0.5779</v>
       </c>
     </row>
     <row r="10">
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159.49</v>
+        <v>158.39</v>
       </c>
       <c r="C10" t="n">
-        <v>147.58</v>
+        <v>147.56</v>
       </c>
       <c r="D10" t="n">
         <v>139.9</v>
       </c>
       <c r="E10" t="n">
-        <v>42.87</v>
+        <v>42.02</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -3426,13 +3426,13 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7856</v>
+        <v>0.7899</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5713</v>
+        <v>0.5798</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6885</v>
+        <v>0.6897</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3658</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="11">
@@ -3472,16 +3472,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>327.5</v>
+        <v>327.25</v>
       </c>
       <c r="C11" t="n">
-        <v>304.4</v>
+        <v>304.39</v>
       </c>
       <c r="D11" t="n">
         <v>208.61</v>
       </c>
       <c r="E11" t="n">
-        <v>45.4</v>
+        <v>45.32</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -3490,10 +3490,10 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.773</v>
+        <v>0.7734</v>
       </c>
       <c r="I11" t="n">
-        <v>0.546</v>
+        <v>0.5468</v>
       </c>
       <c r="J11" t="n">
         <v>0.6883</v>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3893</v>
+        <v>0.3894</v>
       </c>
     </row>
     <row r="12">
@@ -3536,16 +3536,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182.21</v>
+        <v>180.65</v>
       </c>
       <c r="C12" t="n">
-        <v>143.38</v>
+        <v>143.35</v>
       </c>
       <c r="D12" t="n">
-        <v>63.76</v>
+        <v>63.75</v>
       </c>
       <c r="E12" t="n">
-        <v>50.45</v>
+        <v>50.02</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7477</v>
+        <v>0.7499</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4955</v>
+        <v>0.4998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6866</v>
+        <v>0.6871</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>0.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4284</v>
+        <v>0.4285</v>
       </c>
     </row>
     <row r="13">
@@ -3600,16 +3600,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>383.12</v>
+        <v>382.26</v>
       </c>
       <c r="C13" t="n">
-        <v>340.47</v>
+        <v>340.46</v>
       </c>
       <c r="D13" t="n">
-        <v>296.73</v>
+        <v>296.72</v>
       </c>
       <c r="E13" t="n">
-        <v>49.11</v>
+        <v>48.42</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -3618,13 +3618,13 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7579</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5089</v>
+        <v>0.5158</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6835</v>
+        <v>0.6844</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3942</v>
+        <v>0.3944</v>
       </c>
     </row>
     <row r="14">
@@ -3664,16 +3664,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>408.17</v>
+        <v>405.8</v>
       </c>
       <c r="C14" t="n">
-        <v>390.35</v>
+        <v>390.3</v>
       </c>
       <c r="D14" t="n">
-        <v>362.36</v>
+        <v>362.35</v>
       </c>
       <c r="E14" t="n">
-        <v>49.48</v>
+        <v>48.67</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -3682,13 +3682,13 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7526</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5052</v>
+        <v>0.5133</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6813</v>
+        <v>0.6824</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>0.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3834</v>
+        <v>0.3837</v>
       </c>
     </row>
     <row r="15">
@@ -3728,16 +3728,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>264.1</v>
+        <v>262.83</v>
       </c>
       <c r="C15" t="n">
-        <v>243.05</v>
+        <v>243.03</v>
       </c>
       <c r="D15" t="n">
-        <v>230.76</v>
+        <v>230.75</v>
       </c>
       <c r="E15" t="n">
-        <v>39.18</v>
+        <v>38.07</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -3746,13 +3746,13 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8041</v>
+        <v>0.8096</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6082</v>
+        <v>0.6193</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6774</v>
+        <v>0.6794</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>48.88</v>
+        <v>48.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5112</v>
+        <v>0.5127</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>0.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3968</v>
+        <v>0.3973</v>
       </c>
     </row>
     <row r="16">
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>422.61</v>
+        <v>423.02</v>
       </c>
       <c r="C16" t="n">
-        <v>378.98</v>
+        <v>378.99</v>
       </c>
       <c r="D16" t="n">
         <v>349.5</v>
       </c>
       <c r="E16" t="n">
-        <v>47.95</v>
+        <v>48.14</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -3810,13 +3810,13 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7602</v>
+        <v>0.7593</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5205</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6763</v>
+        <v>0.676</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>0.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3353</v>
+        <v>0.3354</v>
       </c>
     </row>
     <row r="17">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.48</v>
+        <v>54.4</v>
       </c>
       <c r="C17" t="n">
         <v>46.05</v>
@@ -3865,7 +3865,7 @@
         <v>32.66</v>
       </c>
       <c r="E17" t="n">
-        <v>56.79</v>
+        <v>56.66</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -3874,10 +3874,10 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7161</v>
+        <v>0.7167</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4321</v>
+        <v>0.4334</v>
       </c>
       <c r="J17" t="n">
         <v>0.6712</v>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0.389</v>
+        <v>0.3891</v>
       </c>
     </row>
     <row r="18">
@@ -3920,16 +3920,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1596.93</v>
+        <v>1592.61</v>
       </c>
       <c r="C18" t="n">
-        <v>1023.77</v>
+        <v>1023.69</v>
       </c>
       <c r="D18" t="n">
-        <v>464.32</v>
+        <v>464.3</v>
       </c>
       <c r="E18" t="n">
-        <v>59.86</v>
+        <v>59.68</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -3938,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7007</v>
+        <v>0.7016</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4014</v>
+        <v>0.4032</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6684</v>
+        <v>0.6686</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>0.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4011</v>
+        <v>0.4013</v>
       </c>
     </row>
     <row r="19">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>384.23</v>
+        <v>383.77</v>
       </c>
       <c r="C19" t="n">
         <v>343.73</v>
@@ -3993,7 +3993,7 @@
         <v>229.64</v>
       </c>
       <c r="E19" t="n">
-        <v>57.37</v>
+        <v>57.26</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -4002,13 +4002,13 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7131</v>
+        <v>0.7137</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4263</v>
+        <v>0.4274</v>
       </c>
       <c r="J19" t="n">
-        <v>0.668</v>
+        <v>0.6681</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3738</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="20">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>216.71</v>
+        <v>216.76</v>
       </c>
       <c r="C20" t="n">
         <v>151.82</v>
@@ -4057,7 +4057,7 @@
         <v>143.63</v>
       </c>
       <c r="E20" t="n">
-        <v>57.49</v>
+        <v>57.51</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -4066,13 +4066,13 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7126</v>
+        <v>0.7124</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4251</v>
+        <v>0.4249</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6677</v>
+        <v>0.6675</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3731</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="21">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>121.44</v>
+        <v>120.94</v>
       </c>
       <c r="C21" t="n">
-        <v>77.95999999999999</v>
+        <v>77.95</v>
       </c>
       <c r="D21" t="n">
         <v>47.68</v>
       </c>
       <c r="E21" t="n">
-        <v>60.46</v>
+        <v>60.15</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -4130,13 +4130,13 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6977</v>
+        <v>0.6992</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3954</v>
+        <v>0.3985</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6656</v>
+        <v>0.666</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>0.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3889</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="22">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>454.14</v>
+        <v>454.23</v>
       </c>
       <c r="C22" t="n">
         <v>401.69</v>
@@ -4185,7 +4185,7 @@
         <v>381.05</v>
       </c>
       <c r="E22" t="n">
-        <v>58.88</v>
+        <v>58.91</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -4194,13 +4194,13 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7056</v>
+        <v>0.7054</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4112</v>
+        <v>0.4109</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6641</v>
+        <v>0.6639</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>411.46</v>
+        <v>411.74</v>
       </c>
       <c r="C23" t="n">
-        <v>374.55</v>
+        <v>374.56</v>
       </c>
       <c r="D23" t="n">
         <v>317.63</v>
       </c>
       <c r="E23" t="n">
-        <v>57.29</v>
+        <v>57.39</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4258,13 +4258,13 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7136</v>
+        <v>0.713</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4271</v>
+        <v>0.4261</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6635</v>
+        <v>0.6632</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4304,16 +4304,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>110.02</v>
+        <v>110.46</v>
       </c>
       <c r="C24" t="n">
-        <v>72.61</v>
+        <v>72.62</v>
       </c>
       <c r="D24" t="n">
-        <v>38.12</v>
+        <v>38.13</v>
       </c>
       <c r="E24" t="n">
-        <v>59.82</v>
+        <v>60.01</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -4322,13 +4322,13 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7009</v>
+        <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4018</v>
+        <v>0.3999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.66</v>
+        <v>0.6597</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4358,26 +4358,26 @@
         <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3449</v>
+        <v>0.3453</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1617.02</v>
+        <v>289.54</v>
       </c>
       <c r="C25" t="n">
-        <v>1439.68</v>
+        <v>267.45</v>
       </c>
       <c r="D25" t="n">
-        <v>1178.48</v>
+        <v>252.13</v>
       </c>
       <c r="E25" t="n">
-        <v>63.3</v>
+        <v>57.84</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -4386,13 +4386,13 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6835</v>
+        <v>0.7108</v>
       </c>
       <c r="I25" t="n">
-        <v>0.367</v>
+        <v>0.4216</v>
       </c>
       <c r="J25" t="n">
-        <v>0.656</v>
+        <v>0.6562</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4422,26 +4422,26 @@
         <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3529</v>
+        <v>0.3005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>290.08</v>
+        <v>1621.55</v>
       </c>
       <c r="C26" t="n">
-        <v>267.46</v>
+        <v>1439.77</v>
       </c>
       <c r="D26" t="n">
-        <v>252.13</v>
+        <v>1178.5</v>
       </c>
       <c r="E26" t="n">
-        <v>58.36</v>
+        <v>63.74</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -4450,13 +4450,13 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.6813</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4164</v>
+        <v>0.3626</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6555</v>
+        <v>0.6552</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>0.5</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3003</v>
+        <v>0.3526</v>
       </c>
     </row>
     <row r="27">
@@ -4496,16 +4496,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>126.84</v>
+        <v>126.54</v>
       </c>
       <c r="C27" t="n">
-        <v>85.20999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D27" t="n">
         <v>62.46</v>
       </c>
       <c r="E27" t="n">
-        <v>68.13</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -4514,13 +4514,13 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6594</v>
+        <v>0.66</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3187</v>
+        <v>0.3201</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6538</v>
+        <v>0.6539</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>0.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3864</v>
+        <v>0.3868</v>
       </c>
     </row>
     <row r="28">
@@ -4560,16 +4560,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>205.37</v>
+        <v>206.2</v>
       </c>
       <c r="C28" t="n">
-        <v>139.83</v>
+        <v>139.85</v>
       </c>
       <c r="D28" t="n">
         <v>96.48</v>
       </c>
       <c r="E28" t="n">
-        <v>68.15000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -4578,13 +4578,13 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6592</v>
+        <v>0.658</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3185</v>
+        <v>0.3159</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6533</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4624,16 +4624,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1985.72</v>
+        <v>1995.58</v>
       </c>
       <c r="C29" t="n">
-        <v>1701.72</v>
+        <v>1701.92</v>
       </c>
       <c r="D29" t="n">
-        <v>1330.41</v>
+        <v>1330.46</v>
       </c>
       <c r="E29" t="n">
-        <v>66.42</v>
+        <v>66.84</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -4642,13 +4642,13 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6679</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3358</v>
+        <v>0.3316</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6518</v>
+        <v>0.6511</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4678,26 +4678,26 @@
         <v>0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3562</v>
+        <v>0.3565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SKYT</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37.24</v>
+        <v>16.8</v>
       </c>
       <c r="C30" t="n">
-        <v>31.47</v>
+        <v>12.65</v>
       </c>
       <c r="D30" t="n">
-        <v>23.05</v>
+        <v>9.59</v>
       </c>
       <c r="E30" t="n">
-        <v>67.98999999999999</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -4706,13 +4706,13 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.66</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3201</v>
+        <v>0.2832</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6504</v>
+        <v>0.6501</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4742,26 +4742,26 @@
         <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3626</v>
+        <v>0.3985</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SKYT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>884.71</v>
+        <v>37.29</v>
       </c>
       <c r="C31" t="n">
-        <v>528.15</v>
+        <v>31.47</v>
       </c>
       <c r="D31" t="n">
-        <v>326.27</v>
+        <v>23.05</v>
       </c>
       <c r="E31" t="n">
-        <v>70.09999999999999</v>
+        <v>68.14</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -4770,13 +4770,13 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6495</v>
+        <v>0.6593</v>
       </c>
       <c r="I31" t="n">
-        <v>0.299</v>
+        <v>0.3186</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6494</v>
+        <v>0.65</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4806,26 +4806,26 @@
         <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3771</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.02</v>
+        <v>884.5599999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>12.66</v>
+        <v>528.14</v>
       </c>
       <c r="D32" t="n">
-        <v>9.59</v>
+        <v>326.27</v>
       </c>
       <c r="E32" t="n">
-        <v>72.86</v>
+        <v>70.09</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -4834,13 +4834,13 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6357</v>
+        <v>0.6496</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2714</v>
+        <v>0.2991</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6484</v>
+        <v>0.6494</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3984</v>
+        <v>0.3778</v>
       </c>
     </row>
     <row r="33">
@@ -4904,7 +4904,7 @@
         <v>0.2477</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6466</v>
+        <v>0.6465</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4944,16 +4944,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>117.75</v>
+        <v>117.35</v>
       </c>
       <c r="C34" t="n">
-        <v>90.56999999999999</v>
+        <v>90.56</v>
       </c>
       <c r="D34" t="n">
-        <v>77.53</v>
+        <v>77.52</v>
       </c>
       <c r="E34" t="n">
-        <v>77.17</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -4962,13 +4962,13 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6142</v>
+        <v>0.6177</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2283</v>
+        <v>0.2354</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6439</v>
+        <v>0.6449</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>0.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0.4111</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="35">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>564.9299999999999</v>
+        <v>565.02</v>
       </c>
       <c r="C35" t="n">
         <v>423.8</v>
@@ -5017,7 +5017,7 @@
         <v>331.03</v>
       </c>
       <c r="E35" t="n">
-        <v>69.29000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -5026,10 +5026,10 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6536</v>
+        <v>0.6535</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3071</v>
+        <v>0.307</v>
       </c>
       <c r="J35" t="n">
         <v>0.6411</v>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3138</v>
+        <v>0.3142</v>
       </c>
     </row>
     <row r="36">
@@ -5072,16 +5072,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>596.86</v>
+        <v>597.23</v>
       </c>
       <c r="C36" t="n">
-        <v>472.43</v>
+        <v>472.44</v>
       </c>
       <c r="D36" t="n">
         <v>383.71</v>
       </c>
       <c r="E36" t="n">
-        <v>69.28</v>
+        <v>69.34</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -5090,13 +5090,13 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6536</v>
+        <v>0.6533</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3072</v>
+        <v>0.3066</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6402</v>
+        <v>0.64</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3074</v>
+        <v>0.3078</v>
       </c>
     </row>
     <row r="37">
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>319.2</v>
+        <v>317.38</v>
       </c>
       <c r="C37" t="n">
-        <v>186.12</v>
+        <v>186.08</v>
       </c>
       <c r="D37" t="n">
-        <v>147.99</v>
+        <v>147.98</v>
       </c>
       <c r="E37" t="n">
-        <v>76.55</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -5154,13 +5154,13 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6173</v>
+        <v>0.6182</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2345</v>
+        <v>0.2365</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6377</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5200,16 +5200,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>319.27</v>
+        <v>315.58</v>
       </c>
       <c r="C38" t="n">
-        <v>177.71</v>
+        <v>177.64</v>
       </c>
       <c r="D38" t="n">
-        <v>171.51</v>
+        <v>171.49</v>
       </c>
       <c r="E38" t="n">
-        <v>78.19</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -5218,13 +5218,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6091</v>
+        <v>0.6113</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2181</v>
+        <v>0.2226</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6359</v>
+        <v>0.6365</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>0.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="39">
@@ -5264,16 +5264,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>749.96</v>
+        <v>749.09</v>
       </c>
       <c r="C39" t="n">
-        <v>698.28</v>
+        <v>698.27</v>
       </c>
       <c r="D39" t="n">
         <v>676.86</v>
       </c>
       <c r="E39" t="n">
-        <v>71.18000000000001</v>
+        <v>70.77</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -5282,13 +5282,13 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6441</v>
+        <v>0.6462</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2882</v>
+        <v>0.2923</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6343</v>
+        <v>0.6349</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2873</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="40">
@@ -5328,16 +5328,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>728.48</v>
+        <v>727.66</v>
       </c>
       <c r="C40" t="n">
-        <v>644.72</v>
+        <v>644.71</v>
       </c>
       <c r="D40" t="n">
         <v>614.4</v>
       </c>
       <c r="E40" t="n">
-        <v>74.12</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -5346,13 +5346,13 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6294</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2588</v>
+        <v>0.261</v>
       </c>
       <c r="J40" t="n">
-        <v>0.629</v>
+        <v>0.6292</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>0.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2813</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="41">
@@ -5392,16 +5392,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>310.52</v>
+        <v>309.74</v>
       </c>
       <c r="C41" t="n">
-        <v>271.57</v>
+        <v>271.56</v>
       </c>
       <c r="D41" t="n">
-        <v>261.55</v>
+        <v>261.54</v>
       </c>
       <c r="E41" t="n">
-        <v>89.61</v>
+        <v>89.36</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -5410,13 +5410,13 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5532</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1039</v>
+        <v>0.1064</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6253</v>
+        <v>0.6256</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>0.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4118</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="42">
@@ -5456,16 +5456,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>225.26</v>
+        <v>224.37</v>
       </c>
       <c r="C42" t="n">
-        <v>146.98</v>
+        <v>146.96</v>
       </c>
       <c r="D42" t="n">
-        <v>142.36</v>
+        <v>142.35</v>
       </c>
       <c r="E42" t="n">
-        <v>90.13</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -5474,10 +5474,10 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5494</v>
+        <v>0.5498</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0987</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0.6233</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4031</v>
+        <v>0.4032</v>
       </c>
     </row>
     <row r="43">
@@ -5520,16 +5520,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>134.72</v>
+        <v>134.09</v>
       </c>
       <c r="C43" t="n">
-        <v>93.27</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="D43" t="n">
         <v>84.39</v>
       </c>
       <c r="E43" t="n">
-        <v>95.7</v>
+        <v>95.64</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -5538,10 +5538,10 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5215</v>
+        <v>0.5218</v>
       </c>
       <c r="I43" t="n">
-        <v>0.043</v>
+        <v>0.0436</v>
       </c>
       <c r="J43" t="n">
         <v>0.6171</v>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>0.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0.4175</v>
+        <v>0.4177</v>
       </c>
     </row>
     <row r="44">
@@ -5584,16 +5584,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>675.21</v>
+        <v>671.95</v>
       </c>
       <c r="C44" t="n">
-        <v>467.5</v>
+        <v>467.43</v>
       </c>
       <c r="D44" t="n">
-        <v>466.46</v>
+        <v>466.44</v>
       </c>
       <c r="E44" t="n">
-        <v>94.5</v>
+        <v>94.41</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -5602,10 +5602,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5275</v>
+        <v>0.528</v>
       </c>
       <c r="I44" t="n">
-        <v>0.055</v>
+        <v>0.0559</v>
       </c>
       <c r="J44" t="n">
         <v>0.6115</v>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N44" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>0.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3683</v>
+        <v>0.3684</v>
       </c>
     </row>
     <row r="45">
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>74.31999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="C45" t="n">
         <v>76.23</v>
@@ -5657,7 +5657,7 @@
         <v>104.35</v>
       </c>
       <c r="E45" t="n">
-        <v>45.26</v>
+        <v>44.91</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -5666,13 +5666,13 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2737</v>
+        <v>0.2755</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5474</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4714</v>
+        <v>0.472</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>0.7</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3286</v>
+        <v>0.3288</v>
       </c>
     </row>
     <row r="46">
@@ -5712,16 +5712,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>431.56</v>
+        <v>432.98</v>
       </c>
       <c r="C46" t="n">
-        <v>389.14</v>
+        <v>389.17</v>
       </c>
       <c r="D46" t="n">
-        <v>410.57</v>
+        <v>410.58</v>
       </c>
       <c r="E46" t="n">
-        <v>64.29000000000001</v>
+        <v>64.63</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -5730,13 +5730,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1785</v>
+        <v>0.1768</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3571</v>
+        <v>0.3537</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4484</v>
+        <v>0.4479</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -5776,16 +5776,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>610.95</v>
+        <v>610.02</v>
       </c>
       <c r="C47" t="n">
-        <v>617.76</v>
+        <v>617.74</v>
       </c>
       <c r="D47" t="n">
         <v>667.9</v>
       </c>
       <c r="E47" t="n">
-        <v>54.07</v>
+        <v>53.46</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -5794,13 +5794,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2296</v>
+        <v>0.2327</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4593</v>
+        <v>0.4654</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4301</v>
+        <v>0.4311</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>0.5</v>
       </c>
       <c r="R47" t="n">
-        <v>0.4082</v>
+        <v>0.4083</v>
       </c>
     </row>
     <row r="48">
@@ -5864,7 +5864,7 @@
         <v>0.5949</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5904,16 +5904,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>242.65</v>
+        <v>241.92</v>
       </c>
       <c r="C49" t="n">
-        <v>244.76</v>
+        <v>244.74</v>
       </c>
       <c r="D49" t="n">
         <v>305.31</v>
       </c>
       <c r="E49" t="n">
-        <v>40.19</v>
+        <v>39.75</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -5922,13 +5922,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2991</v>
+        <v>0.3012</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5981</v>
+        <v>0.6025</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4055</v>
+        <v>0.4061</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>0.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4521</v>
+        <v>0.4523</v>
       </c>
     </row>
     <row r="50">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>47.79</v>
+        <v>47.83</v>
       </c>
       <c r="C50" t="n">
         <v>49.12</v>
@@ -5977,7 +5977,7 @@
         <v>66.23999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>30.41</v>
+        <v>30.55</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -5986,13 +5986,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.348</v>
+        <v>0.3472</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6959</v>
+        <v>0.6945</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4047</v>
+        <v>0.4043</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N50" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>0.5</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3485</v>
+        <v>0.3487</v>
       </c>
     </row>
     <row r="51">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="C51" t="n">
         <v>3.28</v>
@@ -6041,7 +6041,7 @@
         <v>4.3</v>
       </c>
       <c r="E51" t="n">
-        <v>34.38</v>
+        <v>32.31</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -6050,13 +6050,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3281</v>
+        <v>0.3385</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6562</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4002</v>
+        <v>0.4034</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>0.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3583</v>
+        <v>0.3595</v>
       </c>
     </row>
     <row r="52">
@@ -6096,16 +6096,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>89.98999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="C52" t="n">
-        <v>92.34</v>
+        <v>92.33</v>
       </c>
       <c r="D52" t="n">
         <v>94.75</v>
       </c>
       <c r="E52" t="n">
-        <v>43.19</v>
+        <v>42.65</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -6114,13 +6114,13 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2841</v>
+        <v>0.2868</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5681</v>
+        <v>0.5735</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3977</v>
+        <v>0.3984</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N52" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>0.5</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4296</v>
+        <v>0.4299</v>
       </c>
     </row>
     <row r="53">
@@ -6160,16 +6160,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>125.27</v>
+        <v>124.68</v>
       </c>
       <c r="C53" t="n">
-        <v>125.52</v>
+        <v>125.51</v>
       </c>
       <c r="D53" t="n">
         <v>187.15</v>
       </c>
       <c r="E53" t="n">
-        <v>46.91</v>
+        <v>46.43</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -6178,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2654</v>
+        <v>0.2679</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5309</v>
+        <v>0.5357</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3949</v>
+        <v>0.3956</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N53" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>0.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.4486</v>
+        <v>0.4488</v>
       </c>
     </row>
     <row r="54">
@@ -6224,16 +6224,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53.47</v>
+        <v>53.24</v>
       </c>
       <c r="C54" t="n">
-        <v>54.54</v>
+        <v>54.53</v>
       </c>
       <c r="D54" t="n">
         <v>58.42</v>
       </c>
       <c r="E54" t="n">
-        <v>41.28</v>
+        <v>40.92</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -6242,13 +6242,13 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2936</v>
+        <v>0.2954</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5908</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3947</v>
+        <v>0.3951</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>0.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3909</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="55">
@@ -6288,16 +6288,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>305.42</v>
+        <v>304.54</v>
       </c>
       <c r="C55" t="n">
-        <v>293.55</v>
+        <v>293.53</v>
       </c>
       <c r="D55" t="n">
-        <v>323</v>
+        <v>322.99</v>
       </c>
       <c r="E55" t="n">
-        <v>43.38</v>
+        <v>42.92</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -6306,13 +6306,13 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2831</v>
+        <v>0.2854</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5662</v>
+        <v>0.5708</v>
       </c>
       <c r="J55" t="n">
-        <v>0.3943</v>
+        <v>0.395</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6342,26 +6342,26 @@
         <v>0.5</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4094</v>
+        <v>0.4097</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8.31</v>
+        <v>23.32</v>
       </c>
       <c r="C56" t="n">
-        <v>7.7</v>
+        <v>17.73</v>
       </c>
       <c r="D56" t="n">
-        <v>11.46</v>
+        <v>20.41</v>
       </c>
       <c r="E56" t="n">
-        <v>37.17</v>
+        <v>45.02</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -6370,13 +6370,13 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3142</v>
+        <v>0.2749</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6283</v>
+        <v>0.5498</v>
       </c>
       <c r="J56" t="n">
-        <v>0.3929</v>
+        <v>0.3927</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6406,26 +6406,26 @@
         <v>0.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0.3377</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>23.36</v>
+        <v>8.32</v>
       </c>
       <c r="C57" t="n">
-        <v>17.73</v>
+        <v>7.7</v>
       </c>
       <c r="D57" t="n">
-        <v>20.41</v>
+        <v>11.46</v>
       </c>
       <c r="E57" t="n">
-        <v>45.28</v>
+        <v>37.27</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2736</v>
+        <v>0.3136</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5472</v>
+        <v>0.6273</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3924</v>
+        <v>0.3926</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6470,26 +6470,26 @@
         <v>0.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0.4158</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41.02</v>
+        <v>414.09</v>
       </c>
       <c r="C58" t="n">
-        <v>37.34</v>
+        <v>400</v>
       </c>
       <c r="D58" t="n">
-        <v>42.65</v>
+        <v>457.76</v>
       </c>
       <c r="E58" t="n">
-        <v>56.99</v>
+        <v>53.05</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -6498,13 +6498,13 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.215</v>
+        <v>0.2348</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4301</v>
+        <v>0.4695</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3751</v>
+        <v>0.3757</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>0.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4174</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="59">
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11.38</v>
+        <v>11.24</v>
       </c>
       <c r="C59" t="n">
         <v>10.75</v>
       </c>
       <c r="D59" t="n">
-        <v>12.99</v>
+        <v>12.98</v>
       </c>
       <c r="E59" t="n">
-        <v>57.38</v>
+        <v>56.13</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -6562,13 +6562,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2131</v>
+        <v>0.2194</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4262</v>
+        <v>0.4387</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3736</v>
+        <v>0.3755</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6598,26 +6598,26 @@
         <v>0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0.4113</v>
+        <v>0.4117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>416.03</v>
+        <v>41.01</v>
       </c>
       <c r="C60" t="n">
-        <v>400.04</v>
+        <v>37.34</v>
       </c>
       <c r="D60" t="n">
-        <v>457.77</v>
+        <v>42.65</v>
       </c>
       <c r="E60" t="n">
-        <v>54.85</v>
+        <v>56.96</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -6626,13 +6626,13 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2258</v>
+        <v>0.2152</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4515</v>
+        <v>0.4304</v>
       </c>
       <c r="J60" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6662,26 +6662,26 @@
         <v>0.5</v>
       </c>
       <c r="R60" t="n">
-        <v>0.382</v>
+        <v>0.4174</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7.25</v>
+        <v>4.2</v>
       </c>
       <c r="C61" t="n">
-        <v>6.06</v>
+        <v>3.81</v>
       </c>
       <c r="D61" t="n">
-        <v>8.050000000000001</v>
+        <v>5.32</v>
       </c>
       <c r="E61" t="n">
-        <v>53.47</v>
+        <v>51.5</v>
       </c>
       <c r="F61" t="b">
         <v>0</v>
@@ -6690,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2327</v>
+        <v>0.2425</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4653</v>
+        <v>0.485</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3701</v>
+        <v>0.3713</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N61" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6726,26 +6726,26 @@
         <v>0.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0.3487</v>
+        <v>0.3377</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ENVX</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>9.68</v>
+        <v>7.2</v>
       </c>
       <c r="C62" t="n">
-        <v>8.869999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="D62" t="n">
-        <v>13.28</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>53.7</v>
+        <v>52.97</v>
       </c>
       <c r="F62" t="b">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2315</v>
+        <v>0.2352</v>
       </c>
       <c r="I62" t="n">
-        <v>0.463</v>
+        <v>0.4703</v>
       </c>
       <c r="J62" t="n">
-        <v>0.37</v>
+        <v>0.3708</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N62" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6790,26 +6790,26 @@
         <v>0.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3508</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4.24</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>3.81</v>
+        <v>61.87</v>
       </c>
       <c r="D63" t="n">
-        <v>5.33</v>
+        <v>65.42</v>
       </c>
       <c r="E63" t="n">
-        <v>52.53</v>
+        <v>61.84</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2374</v>
+        <v>0.1908</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4747</v>
+        <v>0.3816</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3698</v>
+        <v>0.3706</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N63" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>0.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0.3374</v>
+        <v>0.4363</v>
       </c>
     </row>
     <row r="64">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="C64" t="n">
         <v>11.46</v>
@@ -6873,7 +6873,7 @@
         <v>22.82</v>
       </c>
       <c r="E64" t="n">
-        <v>52.85</v>
+        <v>52.59</v>
       </c>
       <c r="F64" t="b">
         <v>0</v>
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2358</v>
+        <v>0.237</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4715</v>
+        <v>0.4741</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3696</v>
+        <v>0.3699</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6918,26 +6918,26 @@
         <v>0.5</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3391</v>
+        <v>0.3393</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>81.88</v>
+        <v>101.44</v>
       </c>
       <c r="C65" t="n">
-        <v>61.88</v>
+        <v>97.87</v>
       </c>
       <c r="D65" t="n">
-        <v>65.42</v>
+        <v>142.39</v>
       </c>
       <c r="E65" t="n">
-        <v>62.59</v>
+        <v>61.55</v>
       </c>
       <c r="F65" t="b">
         <v>0</v>
@@ -6946,13 +6946,13 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.187</v>
+        <v>0.1923</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3741</v>
+        <v>0.3845</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3695</v>
+        <v>0.3694</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N65" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6982,26 +6982,26 @@
         <v>0.5</v>
       </c>
       <c r="R65" t="n">
-        <v>0.436</v>
+        <v>0.4253</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>512.65</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>449.37</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>534.4</v>
+        <v>13.28</v>
       </c>
       <c r="E66" t="n">
-        <v>57.06</v>
+        <v>54.27</v>
       </c>
       <c r="F66" t="b">
         <v>0</v>
@@ -7010,13 +7010,13 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2147</v>
+        <v>0.2286</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4294</v>
+        <v>0.4573</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3685</v>
+        <v>0.3691</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -7046,26 +7046,26 @@
         <v>0.5</v>
       </c>
       <c r="R66" t="n">
-        <v>0.3739</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>101.89</v>
+        <v>510.42</v>
       </c>
       <c r="C67" t="n">
-        <v>97.88</v>
+        <v>449.33</v>
       </c>
       <c r="D67" t="n">
-        <v>142.39</v>
+        <v>534.39</v>
       </c>
       <c r="E67" t="n">
-        <v>62.24</v>
+        <v>56.66</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -7074,13 +7074,13 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1888</v>
+        <v>0.2167</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3776</v>
+        <v>0.4334</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3684</v>
+        <v>0.369</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -7093,10 +7093,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>0.5</v>
       </c>
       <c r="R67" t="n">
-        <v>0.4251</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="68">
@@ -7120,16 +7120,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="C68" t="n">
-        <v>89.95</v>
+        <v>89.94</v>
       </c>
       <c r="D68" t="n">
         <v>119.41</v>
       </c>
       <c r="E68" t="n">
-        <v>67.3</v>
+        <v>66.89</v>
       </c>
       <c r="F68" t="b">
         <v>0</v>
@@ -7138,13 +7138,13 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1635</v>
+        <v>0.1655</v>
       </c>
       <c r="I68" t="n">
-        <v>0.327</v>
+        <v>0.3311</v>
       </c>
       <c r="J68" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>0.5</v>
       </c>
       <c r="R68" t="n">
-        <v>0.4744</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="69">
@@ -7184,16 +7184,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>192.04</v>
+        <v>191.41</v>
       </c>
       <c r="C69" t="n">
-        <v>167.77</v>
+        <v>167.76</v>
       </c>
       <c r="D69" t="n">
         <v>206.63</v>
       </c>
       <c r="E69" t="n">
-        <v>56.28</v>
+        <v>55.62</v>
       </c>
       <c r="F69" t="b">
         <v>0</v>
@@ -7202,13 +7202,13 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2186</v>
+        <v>0.2219</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4372</v>
+        <v>0.4438</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3641</v>
+        <v>0.365</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -7221,10 +7221,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N69" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>0.5</v>
       </c>
       <c r="R69" t="n">
-        <v>0.3369</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="70">
@@ -7248,16 +7248,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>77.52</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>73.93000000000001</v>
+        <v>73.92</v>
       </c>
       <c r="D70" t="n">
         <v>77.94</v>
       </c>
       <c r="E70" t="n">
-        <v>52.75</v>
+        <v>52.57</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -7266,13 +7266,13 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2362</v>
+        <v>0.2371</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4725</v>
+        <v>0.4743</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3615</v>
+        <v>0.3617</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N70" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>0.5</v>
       </c>
       <c r="R70" t="n">
-        <v>0.2844</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="71">
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>308.17</v>
+        <v>309.5</v>
       </c>
       <c r="C71" t="n">
-        <v>269.47</v>
+        <v>269.5</v>
       </c>
       <c r="D71" t="n">
-        <v>322.79</v>
+        <v>322.8</v>
       </c>
       <c r="E71" t="n">
-        <v>65.29000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F71" t="b">
         <v>0</v>
@@ -7330,13 +7330,13 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1735</v>
+        <v>0.1703</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3471</v>
+        <v>0.3407</v>
       </c>
       <c r="J71" t="n">
-        <v>0.3602</v>
+        <v>0.359</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>0.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0.4011</v>
+        <v>0.4005</v>
       </c>
     </row>
     <row r="72">
@@ -7376,16 +7376,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>251.07</v>
+        <v>250.7</v>
       </c>
       <c r="C72" t="n">
-        <v>236.69</v>
+        <v>236.68</v>
       </c>
       <c r="D72" t="n">
         <v>266.6</v>
       </c>
       <c r="E72" t="n">
-        <v>67.73</v>
+        <v>67.36</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -7394,13 +7394,13 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1614</v>
+        <v>0.1632</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3227</v>
+        <v>0.3264</v>
       </c>
       <c r="J72" t="n">
-        <v>0.3568</v>
+        <v>0.3572</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>63.73</v>
+        <v>63.87</v>
       </c>
       <c r="C73" t="n">
-        <v>41.57</v>
+        <v>41.58</v>
       </c>
       <c r="D73" t="n">
         <v>47.45</v>
       </c>
       <c r="E73" t="n">
-        <v>66.79000000000001</v>
+        <v>66.89</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -7458,13 +7458,13 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.166</v>
+        <v>0.1655</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3321</v>
+        <v>0.3311</v>
       </c>
       <c r="J73" t="n">
-        <v>0.35</v>
+        <v>0.3497</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N73" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -7500,20 +7500,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>36.96</v>
+        <v>379.42</v>
       </c>
       <c r="C74" t="n">
-        <v>28.03</v>
+        <v>317</v>
       </c>
       <c r="D74" t="n">
-        <v>36.03</v>
+        <v>322.73</v>
       </c>
       <c r="E74" t="n">
-        <v>69.94</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="F74" t="b">
         <v>0</v>
@@ -7522,13 +7522,13 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1503</v>
+        <v>0.1673</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3006</v>
+        <v>0.3346</v>
       </c>
       <c r="J74" t="n">
-        <v>0.348</v>
+        <v>0.3473</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -7558,26 +7558,26 @@
         <v>0.5</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3661</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>380.13</v>
+        <v>37.69</v>
       </c>
       <c r="C75" t="n">
-        <v>317.01</v>
+        <v>28.04</v>
       </c>
       <c r="D75" t="n">
-        <v>322.74</v>
+        <v>36.04</v>
       </c>
       <c r="E75" t="n">
-        <v>66.84</v>
+        <v>70.87</v>
       </c>
       <c r="F75" t="b">
         <v>0</v>
@@ -7586,13 +7586,13 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1658</v>
+        <v>0.1456</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3316</v>
+        <v>0.2913</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3469</v>
+        <v>0.3464</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -7605,10 +7605,10 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N75" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -7622,26 +7622,26 @@
         <v>0.5</v>
       </c>
       <c r="R75" t="n">
-        <v>0.3281</v>
+        <v>0.3659</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>97.93000000000001</v>
+        <v>18.56</v>
       </c>
       <c r="C76" t="n">
-        <v>54.69</v>
+        <v>14.73</v>
       </c>
       <c r="D76" t="n">
-        <v>56.85</v>
+        <v>15.6</v>
       </c>
       <c r="E76" t="n">
-        <v>75.20999999999999</v>
+        <v>73.37</v>
       </c>
       <c r="F76" t="b">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.124</v>
+        <v>0.1332</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2479</v>
+        <v>0.2663</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3454</v>
+        <v>0.346</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N76" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -7686,26 +7686,26 @@
         <v>0.5</v>
       </c>
       <c r="R76" t="n">
-        <v>0.4016</v>
+        <v>0.3877</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18.59</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>14.73</v>
+        <v>54.68</v>
       </c>
       <c r="D77" t="n">
-        <v>15.61</v>
+        <v>56.84</v>
       </c>
       <c r="E77" t="n">
-        <v>73.89</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1306</v>
+        <v>0.1245</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2611</v>
+        <v>0.249</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3453</v>
+        <v>0.3455</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N77" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>0.5</v>
       </c>
       <c r="R77" t="n">
-        <v>0.3876</v>
+        <v>0.4017</v>
       </c>
     </row>
     <row r="78">
@@ -7760,16 +7760,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>534.5599999999999</v>
+        <v>532.23</v>
       </c>
       <c r="C78" t="n">
-        <v>456.88</v>
+        <v>456.83</v>
       </c>
       <c r="D78" t="n">
-        <v>470.93</v>
+        <v>470.92</v>
       </c>
       <c r="E78" t="n">
-        <v>70.34999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -7778,13 +7778,13 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1483</v>
+        <v>0.1528</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2965</v>
+        <v>0.3056</v>
       </c>
       <c r="J78" t="n">
-        <v>0.3406</v>
+        <v>0.3419</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N78" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>0.5</v>
       </c>
       <c r="R78" t="n">
-        <v>0.3207</v>
+        <v>0.3209</v>
       </c>
     </row>
     <row r="79">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>189.39</v>
+        <v>189.43</v>
       </c>
       <c r="C79" t="n">
         <v>145.07</v>
@@ -7833,7 +7833,7 @@
         <v>223.66</v>
       </c>
       <c r="E79" t="n">
-        <v>82.09999999999999</v>
+        <v>82.11</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0.0895</v>
       </c>
       <c r="I79" t="n">
-        <v>0.179</v>
+        <v>0.1789</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N79" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>0.5</v>
       </c>
       <c r="R79" t="n">
-        <v>0.4026</v>
+        <v>0.4028</v>
       </c>
     </row>
     <row r="80">
@@ -7888,16 +7888,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>94.39</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>64.05</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="D80" t="n">
-        <v>71.94</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>77.39</v>
+        <v>77.12</v>
       </c>
       <c r="F80" t="b">
         <v>0</v>
@@ -7906,13 +7906,13 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.113</v>
+        <v>0.1144</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2261</v>
+        <v>0.2288</v>
       </c>
       <c r="J80" t="n">
-        <v>0.3345</v>
+        <v>0.3349</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N80" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.3509</v>
+        <v>0.3512</v>
       </c>
     </row>
     <row r="81">
@@ -7952,16 +7952,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>179</v>
+        <v>178.42</v>
       </c>
       <c r="C81" t="n">
-        <v>153.05</v>
+        <v>153.04</v>
       </c>
       <c r="D81" t="n">
-        <v>202.58</v>
+        <v>202.57</v>
       </c>
       <c r="E81" t="n">
-        <v>82.76000000000001</v>
+        <v>82.58</v>
       </c>
       <c r="F81" t="b">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0862</v>
+        <v>0.0871</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1724</v>
+        <v>0.1742</v>
       </c>
       <c r="J81" t="n">
-        <v>0.3313</v>
+        <v>0.3315</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N81" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>0.5</v>
       </c>
       <c r="R81" t="n">
-        <v>0.3828</v>
+        <v>0.3831</v>
       </c>
     </row>
     <row r="82">
@@ -8016,16 +8016,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>258.49</v>
+        <v>257</v>
       </c>
       <c r="C82" t="n">
-        <v>185.81</v>
+        <v>185.78</v>
       </c>
       <c r="D82" t="n">
-        <v>188.03</v>
+        <v>188.02</v>
       </c>
       <c r="E82" t="n">
-        <v>89.58</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -8034,13 +8034,13 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0521</v>
+        <v>0.0591</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1042</v>
+        <v>0.1182</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3228</v>
+        <v>0.3248</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>34.68</v>
+        <v>34.75</v>
       </c>
       <c r="N82" t="n">
-        <v>0.6532</v>
+        <v>0.6525</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>0.5</v>
       </c>
       <c r="R82" t="n">
-        <v>0.3946</v>
+        <v>0.3949</v>
       </c>
     </row>
   </sheetData>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107.09</v>
+        <v>107.39</v>
       </c>
       <c r="D2" t="n">
-        <v>0.831</v>
+        <v>0.8306</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>35.9</v>
+        <v>36.15</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>213.22</v>
+        <v>213.88</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8104</v>
+        <v>0.8094</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>62.39</v>
+        <v>63.01</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.04</v>
+        <v>12.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7965</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -8234,10 +8234,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>35.8</v>
+        <v>36.03</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8357</v>
+        <v>0.8349</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>497.06</v>
+        <v>495.55</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>76.7</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.32</v>
+        <v>13.35</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7554</v>
+        <v>0.7551</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8308,10 +8308,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>59.04</v>
+        <v>59.12</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8357</v>
+        <v>0.8349</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>220.43</v>
+        <v>220.42</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6992</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>40.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -8368,10 +8368,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>189.35</v>
+        <v>188.21</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6904</v>
+        <v>0.6923</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -8382,10 +8382,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>43.81</v>
+        <v>42.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.45999999999999</v>
+        <v>80.37</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6888</v>
+        <v>0.6899</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -8419,10 +8419,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>63.91</v>
+        <v>63.07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>159.49</v>
+        <v>158.48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6885</v>
+        <v>0.6896</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -8456,10 +8456,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>42.87</v>
+        <v>42.09</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>327.5</v>
+        <v>327.19</v>
       </c>
       <c r="D11" t="n">
         <v>0.6883</v>
@@ -8493,10 +8493,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>45.4</v>
+        <v>45.31</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>182.21</v>
+        <v>180.61</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6866</v>
+        <v>0.6871</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8530,10 +8530,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>50.45</v>
+        <v>50.01</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>383.12</v>
+        <v>382.18</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6835</v>
+        <v>0.6845</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>49.11</v>
+        <v>48.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -8590,10 +8590,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>408.17</v>
+        <v>406.01</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6813</v>
+        <v>0.6823</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>49.48</v>
+        <v>48.74</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>264.18</v>
+        <v>262.81</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6773</v>
+        <v>0.6794</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>39.25</v>
+        <v>38.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5111</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>422.61</v>
+        <v>423.05</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6763</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -8678,10 +8678,10 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>47.95</v>
+        <v>48.15</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54.48</v>
+        <v>54.4</v>
       </c>
       <c r="D17" t="n">
         <v>0.6712</v>
@@ -8715,10 +8715,10 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>56.79</v>
+        <v>56.66</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1596.93</v>
+        <v>1593.65</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6684</v>
+        <v>0.6685</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>59.86</v>
+        <v>59.73</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -8775,10 +8775,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>384.23</v>
+        <v>383.77</v>
       </c>
       <c r="D19" t="n">
-        <v>0.668</v>
+        <v>0.6681</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -8789,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>57.37</v>
+        <v>57.26</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>216.71</v>
+        <v>216.76</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6677</v>
+        <v>0.6675</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -8826,10 +8826,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>57.49</v>
+        <v>57.51</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>121.44</v>
+        <v>120.92</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6656</v>
+        <v>0.666</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>60.46</v>
+        <v>60.13</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>454.14</v>
+        <v>454.23</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6641</v>
+        <v>0.6639</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -8900,10 +8900,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>58.88</v>
+        <v>58.91</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -8923,10 +8923,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>411.46</v>
+        <v>411.98</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6635</v>
+        <v>0.6631</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -8937,10 +8937,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>57.29</v>
+        <v>57.48</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -8960,10 +8960,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>110.02</v>
+        <v>110.46</v>
       </c>
       <c r="D24" t="n">
-        <v>0.66</v>
+        <v>0.6597</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -8974,10 +8974,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>59.82</v>
+        <v>60.01</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1617.33</v>
+        <v>289.55</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6559</v>
+        <v>0.6561</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -9011,10 +9011,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>63.33</v>
+        <v>57.86</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9034,10 +9034,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>290.08</v>
+        <v>1622.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6555</v>
+        <v>0.655</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -9048,10 +9048,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>58.36</v>
+        <v>63.83</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>126.84</v>
+        <v>126.61</v>
       </c>
       <c r="D27" t="n">
         <v>0.6538</v>
@@ -9085,10 +9085,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>68.13</v>
+        <v>68.02</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>205.37</v>
+        <v>206.33</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6532</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -9122,10 +9122,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>68.15000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1985.72</v>
+        <v>1995.58</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6518</v>
+        <v>0.6511</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -9159,10 +9159,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>66.42</v>
+        <v>66.84</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SKYT</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37.24</v>
+        <v>16.81</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6504</v>
+        <v>0.65</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -9196,10 +9196,10 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>67.98999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SKYT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9219,10 +9219,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>884.71</v>
+        <v>37.29</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6494</v>
+        <v>0.65</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -9233,10 +9233,10 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>70.09999999999999</v>
+        <v>68.14</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.02</v>
+        <v>884.66</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6484</v>
+        <v>0.6494</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -9270,10 +9270,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>72.86</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>303.27</v>
+        <v>303.54</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6466</v>
+        <v>0.6464</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -9307,10 +9307,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>75.23</v>
+        <v>75.27</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -9330,10 +9330,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>117.75</v>
+        <v>117.37</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6439</v>
+        <v>0.6448</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>77.17</v>
+        <v>76.5</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -9367,10 +9367,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>564.9299999999999</v>
+        <v>565.04</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6411</v>
+        <v>0.641</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>69.29000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>596.86</v>
+        <v>597.23</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6402</v>
+        <v>0.64</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -9418,10 +9418,10 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>69.28</v>
+        <v>69.34</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>319.2</v>
+        <v>316.99</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6378</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -9455,10 +9455,10 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>76.55</v>
+        <v>76.3</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>319.27</v>
+        <v>315.17</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6359</v>
+        <v>0.6365</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -9492,10 +9492,10 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>78.19</v>
+        <v>77.69</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>749.96</v>
+        <v>749.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6343</v>
+        <v>0.6348</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -9529,10 +9529,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>71.18000000000001</v>
+        <v>70.78</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>728.48</v>
+        <v>727.73</v>
       </c>
       <c r="D40" t="n">
-        <v>0.629</v>
+        <v>0.6292</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -9566,10 +9566,10 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>74.12</v>
+        <v>73.92</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>310.45</v>
+        <v>309.69</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6254</v>
+        <v>0.6256</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>89.59</v>
+        <v>89.34</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>225.26</v>
+        <v>224.37</v>
       </c>
       <c r="D42" t="n">
         <v>0.6233</v>
@@ -9640,10 +9640,10 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>90.13</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>134.72</v>
+        <v>134.07</v>
       </c>
       <c r="D43" t="n">
         <v>0.6171</v>
@@ -9677,10 +9677,10 @@
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>95.7</v>
+        <v>95.64</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>675.21</v>
+        <v>672.08</v>
       </c>
       <c r="D44" t="n">
         <v>0.6115</v>
@@ -9714,10 +9714,10 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>94.5</v>
+        <v>94.42</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>74.31999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4714</v>
+        <v>0.4719</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>45.26</v>
+        <v>44.92</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>431.56</v>
+        <v>432.94</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4484</v>
+        <v>0.448</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>64.29000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -9811,10 +9811,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>610.95</v>
+        <v>609.86</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4301</v>
+        <v>0.4312</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>54.07</v>
+        <v>53.35</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
@@ -9851,7 +9851,7 @@
         <v>876</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>40.51</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>242.65</v>
+        <v>241.9</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4055</v>
+        <v>0.4061</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -9899,14 +9899,14 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>40.19</v>
+        <v>39.74</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47.79</v>
+        <v>47.83</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4047</v>
+        <v>0.4043</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>30.41</v>
+        <v>30.55</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -9959,10 +9959,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4002</v>
+        <v>0.4033</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -9973,10 +9973,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>34.38</v>
+        <v>32.31</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>89.98999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3977</v>
+        <v>0.3985</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -10010,10 +10010,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>43.19</v>
+        <v>42.58</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -10033,10 +10033,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>125.27</v>
+        <v>124.68</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3949</v>
+        <v>0.3956</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>46.91</v>
+        <v>46.43</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53.47</v>
+        <v>53.24</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3947</v>
+        <v>0.3951</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>41.28</v>
+        <v>40.92</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>305.42</v>
+        <v>304.61</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3943</v>
+        <v>0.3949</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -10121,10 +10121,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>43.38</v>
+        <v>42.96</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.31</v>
+        <v>23.32</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3929</v>
+        <v>0.3927</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -10158,21 +10158,21 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>37.17</v>
+        <v>45.02</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>potentially oversold</t>
+          <t>balanced opportunity profile</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>23.36</v>
+        <v>8.32</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3924</v>
+        <v>0.3925</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -10195,21 +10195,21 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>45.28</v>
+        <v>37.34</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>41.02</v>
+        <v>414.07</v>
       </c>
       <c r="D58" t="n">
-        <v>0.3751</v>
+        <v>0.3757</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>56.99</v>
+        <v>53.03</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11.38</v>
+        <v>11.25</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3736</v>
+        <v>0.3754</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -10269,10 +10269,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>57.38</v>
+        <v>56.15</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>416.03</v>
+        <v>41.01</v>
       </c>
       <c r="D60" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -10306,10 +10306,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>54.85</v>
+        <v>56.96</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENVX</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7.25</v>
+        <v>4.19</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3701</v>
+        <v>0.3715</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>53.47</v>
+        <v>51.37</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ENVX</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9.68</v>
+        <v>7.18</v>
       </c>
       <c r="D62" t="n">
-        <v>0.37</v>
+        <v>0.3709</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -10380,10 +10380,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>53.7</v>
+        <v>52.89</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4.24</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3698</v>
+        <v>0.3705</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -10417,10 +10417,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>52.53</v>
+        <v>61.84</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>12.39</v>
+        <v>12.35</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3696</v>
+        <v>0.3698</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>52.85</v>
+        <v>52.62</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10477,10 +10477,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>81.88</v>
+        <v>101.45</v>
       </c>
       <c r="D65" t="n">
-        <v>0.3695</v>
+        <v>0.3693</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -10491,10 +10491,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>62.59</v>
+        <v>61.56</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>512.65</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3685</v>
+        <v>0.3691</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -10528,10 +10528,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>57.06</v>
+        <v>54.27</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10551,10 +10551,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>101.89</v>
+        <v>510.5</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3684</v>
+        <v>0.369</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -10565,10 +10565,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>62.24</v>
+        <v>56.68</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -10588,10 +10588,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -10602,10 +10602,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>67.3</v>
+        <v>66.89</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -10625,10 +10625,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>192.04</v>
+        <v>191.32</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3641</v>
+        <v>0.3651</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -10639,10 +10639,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>56.28</v>
+        <v>55.52</v>
       </c>
       <c r="H69" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>77.52</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>0.3615</v>
+        <v>0.3616</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -10676,10 +10676,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>52.75</v>
+        <v>52.59</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>308.17</v>
+        <v>309.5</v>
       </c>
       <c r="D71" t="n">
-        <v>0.3602</v>
+        <v>0.359</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -10713,10 +10713,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>65.29000000000001</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -10736,10 +10736,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>251.07</v>
+        <v>250.7</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3568</v>
+        <v>0.3572</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>67.73</v>
+        <v>67.36</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>63.73</v>
+        <v>63.85</v>
       </c>
       <c r="D73" t="n">
-        <v>0.35</v>
+        <v>0.3497</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>66.79000000000001</v>
+        <v>66.88</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>36.96</v>
+        <v>379.42</v>
       </c>
       <c r="D74" t="n">
-        <v>0.348</v>
+        <v>0.3473</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -10824,10 +10824,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>69.94</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>380.13</v>
+        <v>37.69</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3469</v>
+        <v>0.3464</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>66.84</v>
+        <v>70.87</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>97.93000000000001</v>
+        <v>18.55</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3454</v>
+        <v>0.3461</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -10898,10 +10898,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>75.20999999999999</v>
+        <v>73.31</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>18.59</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3453</v>
+        <v>0.3455</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -10935,10 +10935,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>73.89</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -10958,10 +10958,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>534.5599999999999</v>
+        <v>532.1900000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3406</v>
+        <v>0.3418</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -10972,10 +10972,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>70.34999999999999</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>189.39</v>
+        <v>189.31</v>
       </c>
       <c r="D79" t="n">
         <v>0.3352</v>
@@ -11009,10 +11009,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>82.09999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>94.39</v>
+        <v>93.81</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3345</v>
+        <v>0.335</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>77.39</v>
+        <v>77.02</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -11069,10 +11069,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>179</v>
+        <v>178.41</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3313</v>
+        <v>0.3315</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -11083,10 +11083,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>82.76000000000001</v>
+        <v>82.58</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -11106,10 +11106,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>258.49</v>
+        <v>257</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3228</v>
+        <v>0.3248</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -11120,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>89.58</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6532</v>
+        <v>0.6524</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -11219,25 +11219,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8104</v>
+        <v>0.8094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2532</v>
+        <v>0.2531</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="G2" t="n">
-        <v>7260</v>
+        <v>7250</v>
       </c>
       <c r="H2" t="n">
-        <v>213.22</v>
+        <v>213.88</v>
       </c>
       <c r="I2" t="n">
-        <v>34.05</v>
+        <v>33.9</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4744</v>
+        <v>0.4742</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11280,10 +11280,10 @@
         <v>3480</v>
       </c>
       <c r="H3" t="n">
-        <v>497.06</v>
+        <v>495.55</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.02</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6888</v>
+        <v>0.6899</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1218</v>
+        <v>0.1219</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11326,10 +11326,10 @@
         <v>3320</v>
       </c>
       <c r="H4" t="n">
-        <v>80.45999999999999</v>
+        <v>80.37</v>
       </c>
       <c r="I4" t="n">
-        <v>41.26</v>
+        <v>41.31</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8306</v>
       </c>
       <c r="D5" t="n">
         <v>0.6681</v>
@@ -11372,10 +11372,10 @@
         <v>3310</v>
       </c>
       <c r="H5" t="n">
-        <v>107.02</v>
+        <v>107.39</v>
       </c>
       <c r="I5" t="n">
-        <v>30.93</v>
+        <v>30.82</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6343</v>
+        <v>0.6348</v>
       </c>
       <c r="D6" t="n">
         <v>0.1071</v>
@@ -11418,7 +11418,7 @@
         <v>3110</v>
       </c>
       <c r="H6" t="n">
-        <v>749.98</v>
+        <v>749.1</v>
       </c>
       <c r="I6" t="n">
         <v>4.15</v>
@@ -11449,10 +11449,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6555</v>
+        <v>0.6562</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1526</v>
+        <v>0.1525</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11464,10 +11464,10 @@
         <v>3050</v>
       </c>
       <c r="H7" t="n">
-        <v>290.07</v>
+        <v>289.55</v>
       </c>
       <c r="I7" t="n">
-        <v>10.51</v>
+        <v>10.53</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -11495,10 +11495,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.629</v>
+        <v>0.6292</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1448</v>
+        <v>0.1447</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11510,7 +11510,7 @@
         <v>2950</v>
       </c>
       <c r="H8" t="n">
-        <v>728.54</v>
+        <v>727.73</v>
       </c>
       <c r="I8" t="n">
         <v>4.05</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6835</v>
+        <v>0.6845</v>
       </c>
       <c r="D9" t="n">
         <v>0.2465</v>
@@ -11556,10 +11556,10 @@
         <v>2830</v>
       </c>
       <c r="H9" t="n">
-        <v>383.08</v>
+        <v>382.18</v>
       </c>
       <c r="I9" t="n">
-        <v>7.39</v>
+        <v>7.4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6254</v>
+        <v>0.6257</v>
       </c>
       <c r="D10" t="n">
         <v>0.1764</v>
@@ -11602,10 +11602,10 @@
         <v>2820</v>
       </c>
       <c r="H10" t="n">
-        <v>310.45</v>
+        <v>309.61</v>
       </c>
       <c r="I10" t="n">
-        <v>9.08</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -11633,25 +11633,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6813</v>
+        <v>0.6823</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2504</v>
+        <v>0.2498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="G11" t="n">
-        <v>2800</v>
+        <v>2810</v>
       </c>
       <c r="H11" t="n">
-        <v>408.17</v>
+        <v>406.01</v>
       </c>
       <c r="I11" t="n">
-        <v>6.86</v>
+        <v>6.92</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6641</v>
+        <v>0.6639</v>
       </c>
       <c r="D12" t="n">
         <v>0.2603</v>
@@ -11694,7 +11694,7 @@
         <v>2690</v>
       </c>
       <c r="H12" t="n">
-        <v>454.14</v>
+        <v>454.23</v>
       </c>
       <c r="I12" t="n">
         <v>5.92</v>
@@ -11725,10 +11725,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.644</v>
+        <v>0.6449</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2513</v>
+        <v>0.2516</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11740,10 +11740,10 @@
         <v>2640</v>
       </c>
       <c r="H13" t="n">
-        <v>117.72</v>
+        <v>117.35</v>
       </c>
       <c r="I13" t="n">
-        <v>22.43</v>
+        <v>22.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6401</v>
+        <v>0.64</v>
       </c>
       <c r="D14" t="n">
         <v>0.2473</v>
@@ -11786,7 +11786,7 @@
         <v>2640</v>
       </c>
       <c r="H14" t="n">
-        <v>597.17</v>
+        <v>597.26</v>
       </c>
       <c r="I14" t="n">
         <v>4.42</v>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6634</v>
+        <v>0.6631</v>
       </c>
       <c r="D15" t="n">
         <v>0.2818</v>
@@ -11832,7 +11832,7 @@
         <v>2610</v>
       </c>
       <c r="H15" t="n">
-        <v>411.58</v>
+        <v>411.98</v>
       </c>
       <c r="I15" t="n">
         <v>6.34</v>
@@ -11872,16 +11872,16 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="G16" t="n">
-        <v>2560</v>
+        <v>2550</v>
       </c>
       <c r="H16" t="n">
-        <v>565.21</v>
+        <v>565.04</v>
       </c>
       <c r="I16" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -11909,25 +11909,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6559</v>
+        <v>0.655</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3225</v>
+        <v>0.3224</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="G17" t="n">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="H17" t="n">
-        <v>1617.33</v>
+        <v>1622.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11955,25 +11955,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6171</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2944</v>
+        <v>0.3577</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="G18" t="n">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="H18" t="n">
-        <v>134.72</v>
+        <v>423.05</v>
       </c>
       <c r="I18" t="n">
-        <v>17.74</v>
+        <v>5.63</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -12001,10 +12001,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6764</v>
+        <v>0.6171</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3576</v>
+        <v>0.2944</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12016,10 +12016,10 @@
         <v>2380</v>
       </c>
       <c r="H19" t="n">
-        <v>422.49</v>
+        <v>134.07</v>
       </c>
       <c r="I19" t="n">
-        <v>5.63</v>
+        <v>17.75</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6886</v>
+        <v>0.6897</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3954</v>
+        <v>0.395</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12062,10 +12062,10 @@
         <v>2290</v>
       </c>
       <c r="H20" t="n">
-        <v>159.45</v>
+        <v>158.48</v>
       </c>
       <c r="I20" t="n">
-        <v>14.36</v>
+        <v>14.45</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.6904</v>
+        <v>0.6923</v>
       </c>
       <c r="D21" t="n">
         <v>0.4091</v>
@@ -12108,10 +12108,10 @@
         <v>2240</v>
       </c>
       <c r="H21" t="n">
-        <v>189.35</v>
+        <v>188.21</v>
       </c>
       <c r="I21" t="n">
-        <v>11.83</v>
+        <v>11.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6518</v>
+        <v>0.6511</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3759</v>
+        <v>0.3764</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
         <v>2230</v>
       </c>
       <c r="H22" t="n">
-        <v>1986.08</v>
+        <v>1995.58</v>
       </c>
       <c r="I22" t="n">
         <v>1.12</v>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6538</v>
+        <v>0.6539</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3952</v>
+        <v>0.3948</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12200,10 +12200,10 @@
         <v>2170</v>
       </c>
       <c r="H23" t="n">
-        <v>126.84</v>
+        <v>126.61</v>
       </c>
       <c r="I23" t="n">
-        <v>17.11</v>
+        <v>17.14</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6882</v>
+        <v>0.6883</v>
       </c>
       <c r="D24" t="n">
         <v>0.4362</v>
@@ -12246,10 +12246,10 @@
         <v>2130</v>
       </c>
       <c r="H24" t="n">
-        <v>327.65</v>
+        <v>327.19</v>
       </c>
       <c r="I24" t="n">
-        <v>6.5</v>
+        <v>6.51</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.6466</v>
+        <v>0.6464</v>
       </c>
       <c r="D25" t="n">
         <v>0.431</v>
@@ -12286,16 +12286,16 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="G25" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="H25" t="n">
-        <v>303.23</v>
+        <v>303.54</v>
       </c>
       <c r="I25" t="n">
-        <v>6.66</v>
+        <v>6.62</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -12323,10 +12323,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6532</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4393</v>
+        <v>0.4396</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>2010</v>
       </c>
       <c r="H26" t="n">
-        <v>205.48</v>
+        <v>206.33</v>
       </c>
       <c r="I26" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -12372,19 +12372,19 @@
         <v>0.6115</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4086</v>
+        <v>0.4085</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>1990</v>
+        <v>1980</v>
       </c>
       <c r="H27" t="n">
-        <v>675.45</v>
+        <v>672.08</v>
       </c>
       <c r="I27" t="n">
         <v>2.95</v>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6992</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="D28" t="n">
         <v>0.487</v>
@@ -12424,16 +12424,16 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G28" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="H28" t="n">
-        <v>220.38</v>
+        <v>220.42</v>
       </c>
       <c r="I28" t="n">
-        <v>8.94</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -12461,10 +12461,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.668</v>
+        <v>0.6681</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4872</v>
+        <v>0.4871</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -12476,10 +12476,10 @@
         <v>1880</v>
       </c>
       <c r="H29" t="n">
-        <v>384.28</v>
+        <v>383.77</v>
       </c>
       <c r="I29" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.6502</v>
+        <v>0.65</v>
       </c>
       <c r="D30" t="n">
         <v>0.4868</v>
@@ -12522,10 +12522,10 @@
         <v>1830</v>
       </c>
       <c r="H30" t="n">
-        <v>37.27</v>
+        <v>37.29</v>
       </c>
       <c r="I30" t="n">
-        <v>49.1</v>
+        <v>49.07</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.6375</v>
+        <v>0.6378</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5051</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -12568,10 +12568,10 @@
         <v>1730</v>
       </c>
       <c r="H31" t="n">
-        <v>319.23</v>
+        <v>316.99</v>
       </c>
       <c r="I31" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.6656</v>
+        <v>0.666</v>
       </c>
       <c r="D32" t="n">
         <v>0.5348000000000001</v>
@@ -12614,10 +12614,10 @@
         <v>1700</v>
       </c>
       <c r="H32" t="n">
-        <v>121.48</v>
+        <v>120.92</v>
       </c>
       <c r="I32" t="n">
-        <v>13.99</v>
+        <v>14.06</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>0.6494</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5411</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -12660,7 +12660,7 @@
         <v>1630</v>
       </c>
       <c r="H33" t="n">
-        <v>885.27</v>
+        <v>884.66</v>
       </c>
       <c r="I33" t="n">
         <v>1.84</v>
@@ -12694,7 +12694,7 @@
         <v>0.6233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5407</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -12706,10 +12706,10 @@
         <v>1570</v>
       </c>
       <c r="H34" t="n">
-        <v>225.26</v>
+        <v>224.37</v>
       </c>
       <c r="I34" t="n">
-        <v>6.97</v>
+        <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>0.6712</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5934</v>
+        <v>0.5933</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -12752,10 +12752,10 @@
         <v>1500</v>
       </c>
       <c r="H35" t="n">
-        <v>54.48</v>
+        <v>54.4</v>
       </c>
       <c r="I35" t="n">
-        <v>27.53</v>
+        <v>27.57</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -12783,25 +12783,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.6773</v>
+        <v>0.6794</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2382</v>
+        <v>0.2385</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3477</v>
+        <v>0.3464</v>
       </c>
       <c r="F36" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G36" t="n">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="H36" t="n">
-        <v>264.18</v>
+        <v>262.81</v>
       </c>
       <c r="I36" t="n">
-        <v>5.49</v>
+        <v>5.56</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -12829,10 +12829,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.4484</v>
+        <v>0.448</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3414</v>
+        <v>0.3415</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -12844,10 +12844,10 @@
         <v>1420</v>
       </c>
       <c r="H37" t="n">
-        <v>431.7</v>
+        <v>432.94</v>
       </c>
       <c r="I37" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.4302</v>
+        <v>0.4312</v>
       </c>
       <c r="D38" t="n">
         <v>0.3286</v>
@@ -12884,16 +12884,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G38" t="n">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="H38" t="n">
-        <v>610.84</v>
+        <v>609.86</v>
       </c>
       <c r="I38" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.6684</v>
+        <v>0.6685</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6504</v>
+        <v>0.6503</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -12936,7 +12936,7 @@
         <v>1280</v>
       </c>
       <c r="H39" t="n">
-        <v>1596.51</v>
+        <v>1593.65</v>
       </c>
       <c r="I39" t="n">
         <v>0.8</v>
@@ -12982,10 +12982,10 @@
         <v>960</v>
       </c>
       <c r="H40" t="n">
-        <v>217</v>
+        <v>216.76</v>
       </c>
       <c r="I40" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -13013,10 +13013,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.6359</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7355</v>
+        <v>0.7351</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -13028,10 +13028,10 @@
         <v>920</v>
       </c>
       <c r="H41" t="n">
-        <v>319.26</v>
+        <v>315.17</v>
       </c>
       <c r="I41" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.4715</v>
+        <v>0.4719</v>
       </c>
       <c r="D42" t="n">
         <v>0.6026</v>
@@ -13074,10 +13074,10 @@
         <v>900</v>
       </c>
       <c r="H42" t="n">
-        <v>74.31</v>
+        <v>74.14</v>
       </c>
       <c r="I42" t="n">
-        <v>12.11</v>
+        <v>12.14</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.4066</v>
+        <v>0.4065</v>
       </c>
       <c r="D43" t="n">
         <v>0.3063</v>
@@ -13151,10 +13151,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.6485</v>
+        <v>0.65</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7678</v>
+        <v>0.7679</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -13166,10 +13166,10 @@
         <v>830</v>
       </c>
       <c r="H44" t="n">
-        <v>16.99</v>
+        <v>16.81</v>
       </c>
       <c r="I44" t="n">
-        <v>48.85</v>
+        <v>49.38</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -13197,10 +13197,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.4055</v>
+        <v>0.4061</v>
       </c>
       <c r="D45" t="n">
-        <v>0.3714</v>
+        <v>0.3715</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -13212,10 +13212,10 @@
         <v>800</v>
       </c>
       <c r="H45" t="n">
-        <v>242.66</v>
+        <v>241.9</v>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
@@ -13243,10 +13243,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.66</v>
+        <v>0.6597</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7833</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -13258,10 +13258,10 @@
         <v>780</v>
       </c>
       <c r="H46" t="n">
-        <v>110.02</v>
+        <v>110.46</v>
       </c>
       <c r="I46" t="n">
-        <v>7.09</v>
+        <v>7.06</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.7965</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8845</v>
+        <v>0.8841</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -13304,10 +13304,10 @@
         <v>650</v>
       </c>
       <c r="H47" t="n">
-        <v>12.03</v>
+        <v>12.15</v>
       </c>
       <c r="I47" t="n">
-        <v>54.03</v>
+        <v>53.5</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -13335,10 +13335,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.405</v>
+        <v>0.4042</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5306</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>600</v>
       </c>
       <c r="H48" t="n">
-        <v>47.74</v>
+        <v>47.85</v>
       </c>
       <c r="I48" t="n">
-        <v>12.57</v>
+        <v>12.54</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -13372,34 +13372,34 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AVOID</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.3977</v>
+        <v>0.4034</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2222</v>
+        <v>0.5235</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.24</v>
+        <v>0.6</v>
       </c>
       <c r="G49" t="n">
-        <v>240</v>
+        <v>600</v>
       </c>
       <c r="H49" t="n">
-        <v>89.98</v>
+        <v>2.96</v>
       </c>
       <c r="I49" t="n">
-        <v>2.67</v>
+        <v>202.7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -13411,14 +13411,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>balanced opportunity profile</t>
+          <t>potentially oversold</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13427,25 +13427,25 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.3731</v>
+        <v>0.3985</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2841</v>
+        <v>0.2222</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="G50" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H50" t="n">
-        <v>415.97</v>
+        <v>89.77</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>2.67</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ARKK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13473,25 +13473,25 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.3616</v>
+        <v>0.3757</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2973</v>
+        <v>0.2843</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="G51" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H51" t="n">
-        <v>77.5</v>
+        <v>414.07</v>
       </c>
       <c r="I51" t="n">
-        <v>2.58</v>
+        <v>0.51</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>ARKK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13519,25 +13519,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.347</v>
+        <v>0.3617</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3113</v>
+        <v>0.2973</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G52" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H52" t="n">
-        <v>379.97</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>2.58</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13565,10 +13565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.3695</v>
+        <v>0.3473</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3503</v>
+        <v>0.3112</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -13580,10 +13580,10 @@
         <v>190</v>
       </c>
       <c r="H53" t="n">
-        <v>81.88</v>
+        <v>379.42</v>
       </c>
       <c r="I53" t="n">
-        <v>2.32</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13611,25 +13611,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.357</v>
+        <v>0.3706</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3653</v>
+        <v>0.3504</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G54" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H54" t="n">
-        <v>250.91</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.72</v>
+        <v>2.33</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -13657,10 +13657,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.3944</v>
+        <v>0.3949</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4313</v>
+        <v>0.4311</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -13672,7 +13672,7 @@
         <v>180</v>
       </c>
       <c r="H55" t="n">
-        <v>305.34</v>
+        <v>304.61</v>
       </c>
       <c r="I55" t="n">
         <v>0.59</v>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.3751</v>
+        <v>0.375</v>
       </c>
       <c r="D56" t="n">
         <v>0.3769</v>
@@ -13718,7 +13718,7 @@
         <v>180</v>
       </c>
       <c r="H56" t="n">
-        <v>41.02</v>
+        <v>41.01</v>
       </c>
       <c r="I56" t="n">
         <v>4.39</v>
@@ -13740,7 +13740,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13749,25 +13749,25 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.3406</v>
+        <v>0.3572</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3524</v>
+        <v>0.3654</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="G57" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="H57" t="n">
-        <v>534.5599999999999</v>
+        <v>250.7</v>
       </c>
       <c r="I57" t="n">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13795,25 +13795,25 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.3949</v>
+        <v>0.3419</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4918</v>
+        <v>0.3522</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="G58" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H58" t="n">
-        <v>125.27</v>
+        <v>532.1900000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>1.28</v>
+        <v>0.32</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.3454</v>
+        <v>0.3461</v>
       </c>
       <c r="D59" t="n">
         <v>0.4031</v>
@@ -13856,10 +13856,10 @@
         <v>160</v>
       </c>
       <c r="H59" t="n">
-        <v>18.59</v>
+        <v>18.55</v>
       </c>
       <c r="I59" t="n">
-        <v>8.609999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -13887,10 +13887,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.3228</v>
+        <v>0.3248</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3511</v>
+        <v>0.3513</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -13902,7 +13902,7 @@
         <v>160</v>
       </c>
       <c r="H60" t="n">
-        <v>258.49</v>
+        <v>257</v>
       </c>
       <c r="I60" t="n">
         <v>0.62</v>
@@ -13924,7 +13924,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.3642</v>
+        <v>0.3956</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4651</v>
+        <v>0.492</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -13948,10 +13948,10 @@
         <v>160</v>
       </c>
       <c r="H61" t="n">
-        <v>192.02</v>
+        <v>124.68</v>
       </c>
       <c r="I61" t="n">
-        <v>0.83</v>
+        <v>1.28</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13979,25 +13979,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.3995</v>
+        <v>0.3651</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5234</v>
+        <v>0.4652</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G62" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H62" t="n">
-        <v>3.03</v>
+        <v>191.32</v>
       </c>
       <c r="I62" t="n">
-        <v>49.5</v>
+        <v>0.84</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>potentially oversold</t>
+          <t>balanced opportunity profile</t>
         </is>
       </c>
     </row>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.3345</v>
+        <v>0.335</v>
       </c>
       <c r="D63" t="n">
-        <v>0.475</v>
+        <v>0.4741</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>140</v>
       </c>
       <c r="H63" t="n">
-        <v>94.39</v>
+        <v>93.81</v>
       </c>
       <c r="I63" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.3924</v>
+        <v>0.3927</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5417</v>
+        <v>0.5416</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14086,10 +14086,10 @@
         <v>140</v>
       </c>
       <c r="H64" t="n">
-        <v>23.36</v>
+        <v>23.32</v>
       </c>
       <c r="I64" t="n">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.3682</v>
+        <v>0.3687</v>
       </c>
       <c r="D65" t="n">
         <v>0.5</v>
@@ -14132,7 +14132,7 @@
         <v>140</v>
       </c>
       <c r="H65" t="n">
-        <v>102.48</v>
+        <v>102.24</v>
       </c>
       <c r="I65" t="n">
         <v>1.37</v>
@@ -14163,10 +14163,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.3684</v>
+        <v>0.3693</v>
       </c>
       <c r="D66" t="n">
-        <v>0.5538</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
         <v>130</v>
       </c>
       <c r="H66" t="n">
-        <v>101.86</v>
+        <v>101.45</v>
       </c>
       <c r="I66" t="n">
         <v>1.28</v>
@@ -14200,7 +14200,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>SYM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.3736</v>
+        <v>0.3951</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6017</v>
+        <v>0.6036</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -14224,10 +14224,10 @@
         <v>120</v>
       </c>
       <c r="H67" t="n">
-        <v>11.38</v>
+        <v>53.24</v>
       </c>
       <c r="I67" t="n">
-        <v>10.54</v>
+        <v>2.25</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>120</v>
       </c>
       <c r="H68" t="n">
-        <v>189.33</v>
+        <v>189.31</v>
       </c>
       <c r="I68" t="n">
         <v>0.63</v>
@@ -14292,7 +14292,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SYM</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -14301,10 +14301,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.3947</v>
+        <v>0.3691</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6035</v>
+        <v>0.5874</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -14316,10 +14316,10 @@
         <v>120</v>
       </c>
       <c r="H69" t="n">
-        <v>53.47</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>2.24</v>
+        <v>12.35</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14347,10 +14347,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.37</v>
+        <v>0.3754</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5871</v>
+        <v>0.6012</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -14362,10 +14362,10 @@
         <v>120</v>
       </c>
       <c r="H70" t="n">
-        <v>9.68</v>
+        <v>11.25</v>
       </c>
       <c r="I70" t="n">
-        <v>12.4</v>
+        <v>10.67</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0.3312</v>
+        <v>0.3315</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5682</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -14408,10 +14408,10 @@
         <v>110</v>
       </c>
       <c r="H71" t="n">
-        <v>179.04</v>
+        <v>178.41</v>
       </c>
       <c r="I71" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.3927</v>
+        <v>0.3925</v>
       </c>
       <c r="D72" t="n">
         <v>0.644</v>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.3607</v>
+        <v>0.359</v>
       </c>
       <c r="D73" t="n">
-        <v>0.602</v>
+        <v>0.6016</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         <v>110</v>
       </c>
       <c r="H73" t="n">
-        <v>307.47</v>
+        <v>309.5</v>
       </c>
       <c r="I73" t="n">
         <v>0.36</v>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.3701</v>
+        <v>0.3709</v>
       </c>
       <c r="D74" t="n">
-        <v>0.6428</v>
+        <v>0.6417</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -14546,10 +14546,10 @@
         <v>100</v>
       </c>
       <c r="H74" t="n">
-        <v>7.25</v>
+        <v>7.18</v>
       </c>
       <c r="I74" t="n">
-        <v>13.79</v>
+        <v>13.93</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14577,10 +14577,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.3684</v>
+        <v>0.369</v>
       </c>
       <c r="D75" t="n">
-        <v>0.653</v>
+        <v>0.6526</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -14592,7 +14592,7 @@
         <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>512.8200000000001</v>
+        <v>510.5</v>
       </c>
       <c r="I75" t="n">
         <v>0.2</v>
@@ -14623,10 +14623,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.348</v>
+        <v>0.3464</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6567</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -14638,10 +14638,10 @@
         <v>90</v>
       </c>
       <c r="H76" t="n">
-        <v>36.98</v>
+        <v>37.69</v>
       </c>
       <c r="I76" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -14669,10 +14669,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.3698</v>
+        <v>0.3715</v>
       </c>
       <c r="D77" t="n">
-        <v>0.6871</v>
+        <v>0.6869</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>90</v>
       </c>
       <c r="H77" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="I77" t="n">
-        <v>21.23</v>
+        <v>21.48</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.6865</v>
+        <v>0.6871</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9813</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -14730,10 +14730,10 @@
         <v>70</v>
       </c>
       <c r="H78" t="n">
-        <v>182.26</v>
+        <v>180.61</v>
       </c>
       <c r="I78" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.35</v>
+        <v>0.3497</v>
       </c>
       <c r="D79" t="n">
         <v>0.754</v>
@@ -14776,7 +14776,7 @@
         <v>70</v>
       </c>
       <c r="H79" t="n">
-        <v>63.69</v>
+        <v>63.85</v>
       </c>
       <c r="I79" t="n">
         <v>1.1</v>
@@ -14807,10 +14807,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.3696</v>
+        <v>0.3698</v>
       </c>
       <c r="D80" t="n">
-        <v>0.8041</v>
+        <v>0.8038</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -14822,10 +14822,10 @@
         <v>60</v>
       </c>
       <c r="H80" t="n">
-        <v>12.39</v>
+        <v>12.35</v>
       </c>
       <c r="I80" t="n">
-        <v>4.84</v>
+        <v>4.86</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
